--- a/app/reports/SRCE_research.xlsx
+++ b/app/reports/SRCE_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-29 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-02 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.832</v>
+        <v>0.831</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>181.44</v>
+        <v>181.97</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>84.39</v>
+        <v>86.22</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.15</v>
+        <v>1.111</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.994</v>
+        <v>0.991</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.05276999950408936</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>24081826.56712881</v>
+        <v>24081826.76873115</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>84.39</v>
+        <v>86.22</v>
       </c>
     </row>
     <row r="38">
@@ -1520,14 +1520,14 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>2032265344</v>
+        <v>2076335104</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>12.11</v>
+        <v>12.37</v>
       </c>
       <c r="E5" s="32" t="n"/>
       <c r="F5" s="32" t="n">
-        <v>5.13</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="6">
@@ -1542,14 +1542,14 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>2044361344</v>
+        <v>2060025088</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>12.335365</v>
+        <v>12.429878</v>
       </c>
       <c r="E6" s="34" t="n"/>
       <c r="F6" s="34" t="n">
-        <v>4.327</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="7">
@@ -1564,14 +1564,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>2507660800</v>
+        <v>2505776896</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>12.839229</v>
+        <v>12.829583</v>
       </c>
       <c r="E7" s="34" t="n"/>
       <c r="F7" s="34" t="n">
-        <v>5.524</v>
+        <v>5.446</v>
       </c>
     </row>
     <row r="8">
@@ -1586,14 +1586,14 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>1828209024</v>
+        <v>1844368000</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>12.802632</v>
+        <v>12.915791</v>
       </c>
       <c r="E8" s="34" t="n"/>
       <c r="F8" s="34" t="n">
-        <v>5.093</v>
+        <v>5.038</v>
       </c>
     </row>
     <row r="9">
@@ -1608,14 +1608,14 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>1438771840</v>
+        <v>1455302144</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>13.275229</v>
+        <v>13.427752</v>
       </c>
       <c r="E9" s="34" t="n"/>
       <c r="F9" s="34" t="n">
-        <v>4.912</v>
+        <v>4.852</v>
       </c>
     </row>
     <row r="10">
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>1692129152</v>
+        <v>1695831808</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>12.783217</v>
+        <v>12.811189</v>
       </c>
       <c r="E10" s="34" t="n"/>
       <c r="F10" s="34" t="n">
-        <v>1.85</v>
+        <v>1.817</v>
       </c>
     </row>
     <row r="11">
@@ -1652,14 +1652,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>2291850496</v>
+        <v>2302186752</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>10.018072</v>
+        <v>10.063253</v>
       </c>
       <c r="E11" s="34" t="n"/>
       <c r="F11" s="34" t="n">
-        <v>10.163</v>
+        <v>10.015</v>
       </c>
     </row>
     <row r="12">
@@ -1674,14 +1674,14 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>1744614016</v>
+        <v>1699851904</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>16.457981</v>
+        <v>16.035713</v>
       </c>
       <c r="E12" s="34" t="n"/>
       <c r="F12" s="34" t="n">
-        <v>3.777</v>
+        <v>3.731</v>
       </c>
     </row>
     <row r="13">
@@ -1696,14 +1696,14 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>1705439232</v>
+        <v>1737707136</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>13.035041</v>
+        <v>13.105054</v>
       </c>
       <c r="E13" s="34" t="n"/>
       <c r="F13" s="34" t="n">
-        <v>4.426</v>
+        <v>4.417</v>
       </c>
     </row>
     <row r="15">
